--- a/data/input/Flujos.xlsx
+++ b/data/input/Flujos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\prueba_Tecnica\desarrollo\desarrollo_python\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E3F9C10-DBCC-442D-8DFB-74409E226A28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67D0ED88-D143-4FE9-A337-050A7E25A7A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -167,7 +167,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -176,6 +176,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -204,9 +212,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -510,7 +519,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="22.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="10" max="10" width="22.5703125" style="1"/>
@@ -1005,7 +1014,7 @@
       <c r="F11" t="s">
         <v>14</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H11" t="s">
@@ -1596,6 +1605,9 @@
       <c r="O23" t="s">
         <v>18</v>
       </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N31" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
